--- a/results/Int All Data -0.9/Linea_fi_all.xlsx
+++ b/results/Int All Data -0.9/Linea_fi_all.xlsx
@@ -2326,7 +2326,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>-0.002536125036862258 +/- 0.0017154868265702352</t>
+          <t>-0.0025656148628722788 +/- 0.0017597792683970272</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>-0.00014744913005010352 +/- 0.0004800595870274173</t>
+          <t>-0.0001769389560601242 +/- 0.00047915295810297694</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>-0.001006214856466392 +/- 0.0010353865454001531</t>
+          <t>-0.0009470257472624866 +/- 0.0010977944356905043</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.0005022156573116998 +/- 0.0017579409804209286</t>
+          <t>0.0005317577548006214 +/- 0.0017911381259940193</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>-0.0017549357568161007 +/- 0.0005978935765697137</t>
+          <t>-0.0017235976183015201 +/- 0.0005472970603752197</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>0.008367282983390734 +/- 0.0021440875566402155</t>
+          <t>0.008335944844876163 +/- 0.00216754828778321</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0011788977306219084 +/- 0.0007219244747371487</t>
+          <t>0.0012378426171529954 +/- 0.0007662835249042133</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.003684055408193376 +/- 0.0030917983693976307</t>
+          <t>0.0037430002947244747 +/- 0.0030487956939994148</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.012673150604185123 +/- 0.0024015972634793365</t>
+          <t>0.012525788387857395 +/- 0.0024877605387760332</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.004715590922487511 +/- 0.0014558313038878252</t>
+          <t>0.004686118479221968 +/- 0.001476272300190767</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.000854700854700885 +/- 0.0020008728644260116</t>
+          <t>0.0008841732979664396 +/- 0.0020248233465744447</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>-0.00627763041556142 +/- 0.0017881298334356127</t>
+          <t>-0.006218685529030321 +/- 0.0018093775983696963</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.012319481284998556 +/- 0.0024188959067118375</t>
+          <t>0.012525788387857395 +/- 0.0024877605387760332</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.0026525198938992522 +/- 0.000632113486281374</t>
+          <t>0.0027704096669614263 +/- 0.0006746550629094863</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -6771,17 +6771,17 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0.005835543766578277 +/- 0.0008822062804064488</t>
+          <t>0.005717653993516081 +/- 0.00085622393435507</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0.009637488947833828 +/- 0.001919332762176816</t>
+          <t>0.009666961391099372 +/- 0.0019540918896847215</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-0.00041261420571763184 +/- 0.000915070715959925</t>
+          <t>-0.0005010315355142625 +/- 0.0008846643689834256</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.0188918361332155 +/- 0.00281288185386096</t>
+          <t>0.018921308576481034 +/- 0.002829354553492482</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.00999115826702036 +/- 0.0022655473081022778</t>
+          <t>0.010020630710285916 +/- 0.0022484209988518243</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-0.00020630710285879372 +/- 0.00029619438906927344</t>
+          <t>5.89448865311204e-05 +/- 0.00017683465959330568</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.009725906277630458 +/- 0.001977071598143033</t>
+          <t>0.009666961391099372 +/- 0.0019540918896847215</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>0.0006483937518420802 +/- 0.00039099614386740254</t>
+          <t>0.0006778661951076015 +/- 0.00039651117144335127</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -6881,17 +6881,17 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>-0.0003536693191865337 +/- 0.0004331546848422998</t>
+          <t>-0.000324196875920979 +/- 0.0004650673102876497</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0.004509283819628673 +/- 0.001473916858243454</t>
+          <t>0.00447981137636313 +/- 0.0014605967218819917</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-0.004391394046566443 +/- 0.0016953701170963377</t>
+          <t>-0.004391394046566433 +/- 0.001794917769358695</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-0.007515473032714393 +/- 0.0018698169084069415</t>
+          <t>-0.007721780135573231 +/- 0.0019091228695197924</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>0.004509283819628685 +/- 0.0015146083298001219</t>
+          <t>0.00447981137636313 +/- 0.0014605967218819917</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.001267315060418528 +/- 0.0008022786671863473</t>
+          <t>0.0014146772767462679 +/- 0.0008723046617712092</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>0.01889183613321547 +/- 0.001956979110054126</t>
+          <t>0.017889773062186875 +/- 0.0019328620609572152</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -7001,17 +7001,17 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>-0.008163866784556406 +/- 0.001964068032012494</t>
+          <t>-0.007810197465369861 +/- 0.001969367977870681</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>-0.003241968759210112 +/- 0.0010626440540713385</t>
+          <t>-0.0030651340996168284 +/- 0.0010560844601927</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>-0.002623047450633631 +/- 0.0008278556973290928</t>
+          <t>-0.0030651340996168284 +/- 0.0010560844601927</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -7021,12 +7021,12 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>0.0038608900677866596 +/- 0.0022229725874604285</t>
+          <t>0.0038903625110521924 +/- 0.0023086538199311828</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>-0.0009136457412319387 +/- 0.0006382672510376513</t>
+          <t>-0.0009431181844974823 +/- 0.0006430127977975604</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>-8.841732979659733e-05 +/- 0.00037396338168139146</t>
+          <t>0.0007073386383731562 +/- 0.00037743143161993284</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>0.0486884762746832 +/- 0.003154515333983996</t>
+          <t>0.048659003831417656 +/- 0.0031035756233127624</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>0.009401709401709424 +/- 0.005024943538798825</t>
+          <t>0.009313292071912782 +/- 0.004944348240615577</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>-0.0016504568228705829 +/- 0.00311405339036187</t>
+          <t>-0.0015915119363394958 +/- 0.0031884770613141294</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -7131,12 +7131,12 @@
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>0.05487768936044801 +/- 0.0036759120135971433</t>
+          <t>0.05517241379310346 +/- 0.0036163540583973946</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>0.1464780430297672 +/- 0.005421647998852656</t>
+          <t>0.14615384615384622 +/- 0.005508193855763927</t>
         </is>
       </c>
       <c r="CZ9" t="inlineStr">
@@ -7211,17 +7211,17 @@
       </c>
       <c r="DN9" t="inlineStr">
         <is>
-          <t>0.020306513409961723 +/- 0.002026752873204157</t>
+          <t>0.020542292956086106 +/- 0.0019373508316586742</t>
         </is>
       </c>
       <c r="DO9" t="inlineStr">
         <is>
-          <t>0.05278514588859421 +/- 0.0030442337601708667</t>
+          <t>0.053050397877984115 +/- 0.0031329636937031087</t>
         </is>
       </c>
       <c r="DP9" t="inlineStr">
         <is>
-          <t>0.0029472443265546877 +/- 0.0008017371357934198</t>
+          <t>0.0028293545534925023 +/- 0.0006999317469518349</t>
         </is>
       </c>
       <c r="DQ9" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="DR9" t="inlineStr">
         <is>
-          <t>0.0005599764220454051 +/- 0.0004650673102876335</t>
+          <t>0.0006189213085765032 +/- 0.0004650673102876229</t>
         </is>
       </c>
       <c r="DS9" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="DX9" t="inlineStr">
         <is>
-          <t>-0.010138520483348035 +/- 0.0009522837855233505</t>
+          <t>-0.010167992926613589 +/- 0.000979709409878863</t>
         </is>
       </c>
       <c r="DY9" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="EB9" t="inlineStr">
         <is>
-          <t>0.05319776009431184 +/- 0.0032345922564570983</t>
+          <t>0.053050397877984115 +/- 0.0031329636937031087</t>
         </is>
       </c>
       <c r="EC9" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="EJ9" t="inlineStr">
         <is>
-          <t>0.007603890362511079 +/- 0.0011245967597016855</t>
+          <t>0.007780725022104362 +/- 0.0011655596777651162</t>
         </is>
       </c>
       <c r="EK9" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="EN9" t="inlineStr">
         <is>
-          <t>0.0003536693191865892 +/- 0.0005714918782689344</t>
+          <t>0.0003831417624521327 +/- 0.000604723976677945</t>
         </is>
       </c>
       <c r="EO9" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="EQ9" t="inlineStr">
         <is>
-          <t>-0.004273504273504258 +/- 0.001620984379605079</t>
+          <t>-0.0043029767167698015 +/- 0.0016578085600265579</t>
         </is>
       </c>
       <c r="ER9" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="DX10" t="inlineStr">
         <is>
-          <t>0.004177470469605293 +/- 0.001309198244598295</t>
+          <t>0.004206280610774993 +/- 0.001334005981306854</t>
         </is>
       </c>
       <c r="DY10" t="inlineStr">
